--- a/AAII_Financials/Quarterly/FLT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FLT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
   <si>
     <t>FLT</t>
   </si>
@@ -656,255 +656,261 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>937300</v>
+      </c>
+      <c r="E8" s="3">
         <v>970900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>948200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>901300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>883600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>893000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>861300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>789200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>802300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>755500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>667400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>608600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>617300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>585300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>525100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>661100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>698900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>681000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>647100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>621800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>643400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>619600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>585000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>585500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>610000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>577900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>541200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>520400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>515000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>484400</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>201500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>208200</v>
+      </c>
+      <c r="F9" s="3">
+        <v>205300</v>
+      </c>
+      <c r="G9" s="3">
+        <v>205000</v>
+      </c>
+      <c r="H9" s="3">
+        <v>201600</v>
+      </c>
+      <c r="I9" s="3">
+        <v>203300</v>
+      </c>
+      <c r="J9" s="3">
+        <v>185600</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -954,49 +960,52 @@
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB9" s="3">
         <v>30400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>27700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>30600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>24400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>25600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>28200</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>735800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>762700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>742900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>696300</v>
+      </c>
+      <c r="H10" s="3">
+        <v>682000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>689700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>675700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1046,26 +1055,29 @@
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB10" s="3">
         <v>579600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>550200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>510600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>496000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>489400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>456200</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,49 +1298,52 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>16200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>5</v>
@@ -1332,11 +1351,11 @@
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>5</v>
@@ -1344,130 +1363,136 @@
       <c r="V14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>2100</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>3300</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>83900</v>
+      </c>
+      <c r="E15" s="3">
         <v>84800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>83700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>84200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>89800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>77200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>78500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>76800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>75000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>74200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>69200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>65700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>64700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>63500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>62200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>64500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>68500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>67300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>70900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>67400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>67200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>67300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>68600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>71500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>65800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>69200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>64700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>64900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>61400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>57100</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>513300</v>
+      </c>
+      <c r="E17" s="3">
         <v>525900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>535500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>526100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>514300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>503800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>490800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>471500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>478200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>416800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>369800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>342700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>323400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>320800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>312300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>460100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>378100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>351900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>349800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>337600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>360800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>338500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>320200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>325400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>370000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>348500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>325200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>325400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>299000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>293400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>424000</v>
+      </c>
+      <c r="E18" s="3">
         <v>445000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>412700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>375200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>369300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>389200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>370500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>317700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>324100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>338700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>297600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>265900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>293900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>264500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>212800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>201000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>320800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>329100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>297300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>284200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>282600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>281100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>264800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>260100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>240000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>229400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>216000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>195000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>216000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>191000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,192 +1747,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-90500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-74900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-86100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-80300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-71800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-49300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-26800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-23000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-21700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-30600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-35100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-30300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-30700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-29100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-28700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-22300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-36300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-40100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-54900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>114400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-43500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-33600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-30800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-31700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>98100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-25600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-27700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-62600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-20800</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>417400</v>
+      </c>
+      <c r="E21" s="3">
         <v>454800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>410200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>379100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>387200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>417100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>422100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>371500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>377500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>382400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>331700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>301400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>327900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>298900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>273800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>236800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>367100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>360100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>328200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>296700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>463200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>303200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>298500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>299600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>272800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>395000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>253600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>230700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>213400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>225900</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,192 +2030,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>333500</v>
+      </c>
+      <c r="E23" s="3">
         <v>370100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>326600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>294800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>297400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>339900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>343700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>294700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>302500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>308100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>262500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>235700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>263200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>235400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>211600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>172300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>298600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>292800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>257300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>229200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>397100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>237600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>231200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>229300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>208300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>327500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>190400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>167400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>153500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>170200</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>77600</v>
+      </c>
+      <c r="E24" s="3">
         <v>98600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>86900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>80000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>72100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>91000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>81500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>76700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>77500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>74100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>66300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>51400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>53300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>46600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>53100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>25200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>63100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>67000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-4400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>57100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>93300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>57100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>54300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>54400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>53800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>124700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>59400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>43700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>58000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>40600</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>255900</v>
+      </c>
+      <c r="E26" s="3">
         <v>271500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>239700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>214800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>225300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>248900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>262200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>218000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>225000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>234000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>196200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>184200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>209900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>188800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>158500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>147100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>235500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>225800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>261700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>172100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>303800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>180400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>176900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>174900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>154600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>202800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>131000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>123700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>95400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>129600</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>255900</v>
+      </c>
+      <c r="E27" s="3">
         <v>271500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>239700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>214800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>225300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>248900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>262200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>218000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>225000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>234000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>196200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>184200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>209900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>188800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>158500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>147100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>235500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>225800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>261700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>172100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>303800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>180400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>176900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>174900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>154600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>202800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>131000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>123700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>95400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>129600</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2587,8 +2647,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>5</v>
@@ -2605,24 +2665,24 @@
       <c r="V29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3">
         <v>-1800</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-22700</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>128100</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>90500</v>
+      </c>
+      <c r="E32" s="3">
         <v>74900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>86100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>80300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>71800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>49300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>26800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>23000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>21700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>30600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>35100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>30300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>30700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>29100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>28700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>22300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>36300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>40100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>54900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-114400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>43500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>33600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>30800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>31700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-98100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>25600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>27700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>62600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>255900</v>
+      </c>
+      <c r="E33" s="3">
         <v>271500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>239700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>214800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>225300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>248900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>262200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>218000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>225000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>234000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>196200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>184200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>209900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>188800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>158500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>147100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>235500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>225800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>261700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>172100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>302000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>157700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>176900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>174900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>282700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>202800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>131000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>123700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>95400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>129600</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>255900</v>
+      </c>
+      <c r="E35" s="3">
         <v>271500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>239700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>214800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>225300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>248900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>262200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>218000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>225000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>234000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>196200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>184200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>209900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>188800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>158500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>147100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>235500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>225800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>261700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>172100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>302000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>157700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>176900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>174900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>282700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>202800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>131000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>123700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>95400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>129600</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1389600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1094200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1254200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1272500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1435200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1317500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1423100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1298200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1520000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1271000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1301200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>958300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>934900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>788900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>765800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1070700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1271500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1058800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1170300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1057500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1031100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>924400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>919700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>979600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>913600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>834800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>564600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>546600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>475000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>405400</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,100 +3625,106 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3468600</v>
+      </c>
+      <c r="E43" s="3">
         <v>4051300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3708700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3653200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3351700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3666600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4048600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3740600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2911300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3169500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2787200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2505600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2066800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2240700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1933300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2157100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2539900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2696000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2701200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2597500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2311800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2742300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2655900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2520800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2231000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2250300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2170600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2036800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1793000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1990700</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,221 +3815,230 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2226000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1714700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1960700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1433300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1319200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1601900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1351800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1137400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1056700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1083800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1165800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>821400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>954600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>941500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>764900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>901300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>807100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>685200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>514800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>517100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>533000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>466200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>473600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>406700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>405100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>436500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>310200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>298700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>259700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>289000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7084300</v>
+      </c>
+      <c r="E46" s="3">
         <v>6860300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6923600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6359000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6106200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6586100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6823500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6176200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5488000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5524300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5254100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4285400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3956300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3971000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3464100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4129000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4618600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4440000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4386400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4172100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3876000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4133000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4049200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3907100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3549700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3521500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3045400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2882100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2527700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2685200</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E47" s="3">
         <v>68000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>69700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>67600</v>
-      </c>
-      <c r="G47" s="3">
-        <v>74300</v>
       </c>
       <c r="H47" s="3">
         <v>74300</v>
       </c>
       <c r="I47" s="3">
+        <v>74300</v>
+      </c>
+      <c r="J47" s="3">
         <v>67100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>71100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>52000</v>
-      </c>
-      <c r="L47" s="3">
-        <v>11900</v>
       </c>
       <c r="M47" s="3">
         <v>11900</v>
@@ -3943,245 +4047,254 @@
         <v>11900</v>
       </c>
       <c r="O47" s="3">
-        <v>7500</v>
+        <v>11900</v>
       </c>
       <c r="P47" s="3">
         <v>7500</v>
       </c>
       <c r="Q47" s="3">
+        <v>7500</v>
+      </c>
+      <c r="R47" s="3">
         <v>61800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>28100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>30400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>26300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>26600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>26500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>42700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>33000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>39900</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>32900</v>
       </c>
       <c r="AA47" s="3">
         <v>32900</v>
       </c>
       <c r="AB47" s="3">
+        <v>32900</v>
+      </c>
+      <c r="AC47" s="3">
         <v>33500</v>
-      </c>
-      <c r="AC47" s="3">
-        <v>40800</v>
       </c>
       <c r="AD47" s="3">
         <v>40800</v>
       </c>
       <c r="AE47" s="3">
+        <v>40800</v>
+      </c>
+      <c r="AF47" s="3">
         <v>36200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>79700</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>343200</v>
+      </c>
+      <c r="E48" s="3">
         <v>330000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>329100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>310400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>294700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>272600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>260600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>254400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>236300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>220600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>216700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>200200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>279300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>190000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>185600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>265300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>255700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>241400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>264700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>186300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>186200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>185000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>179100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>184000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>180100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>168100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>154300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>149000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>142500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>144500</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7730600</v>
+      </c>
+      <c r="E49" s="3">
         <v>7718500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7580700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7577600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7332400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7238200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7296600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7495200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7414400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7471700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7323700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6744400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6835100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6728800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6703600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6753600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7174900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7023000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7137700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6904700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6950000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6956000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7071400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7426800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7440800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7521000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>6774800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>6861100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>6848400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6942900</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>248700</v>
+      </c>
+      <c r="E52" s="3">
         <v>287700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>275500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>273300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>281700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>314800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>262500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>224500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>213900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>225900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>220500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>185700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>116400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>196800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>211700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>134100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>168900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>183500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>160200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>225400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>147600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>143900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>145500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>141700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>115000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>86200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>86400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>76900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>72000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>63800</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15476300</v>
+      </c>
+      <c r="E54" s="3">
         <v>15264500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15178700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14587900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14089300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14486000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14710200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14221400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13404700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13454400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13026900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11427500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11194600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11094000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10626700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11310200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12248500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>11914200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>11975600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>11514900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>11202500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>11450900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>11485100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11692500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>11318400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11330300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>10101700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>10010000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9626700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9916100</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4837,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1625000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1895300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1679700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1907800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1568900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1694000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2015000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1957100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1406400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1726700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1578300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1349000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1054500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1297200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1096300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1058700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1249600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1375900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1523900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1518800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1117600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1616900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1532700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1609200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1437300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1435600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1240800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1246200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1151400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1230300</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2126700</v>
+      </c>
+      <c r="E58" s="3">
         <v>2345800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2071200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2097100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2314100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2476100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2108100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1927000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1517600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1901400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1346100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1364200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1205700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1333800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1245200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1913500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1746800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1165200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1932400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1807300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2070600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1699500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1915700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1621900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1616500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1602500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1443400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1407700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1336500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1383800</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3074000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2497100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2685000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2198600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2160500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2468100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2308800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2207900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2366400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2038200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2056100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1600800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1708100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1564800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1285500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1487900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1466600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1437800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1293000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1236000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1306900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1168000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1153100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1076500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1041700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1134800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>934800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>846800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>808400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>840900</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6825800</v>
+      </c>
+      <c r="E60" s="3">
         <v>6738200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6435900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6203500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6043500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6638200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6431900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6091900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5290400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5666300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4980400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4314000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3968300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4195800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3627000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4460100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4463100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3978900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4749200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4562100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4495200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4484500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4601500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4307700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4095500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4172900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3619000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3500700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3296300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3455000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4596200</v>
+      </c>
+      <c r="E61" s="3">
         <v>4637200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4678300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4700600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4722800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4745100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4767500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4416400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4460000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3790000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3732700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3082000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3126900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3158800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3202500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3246200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3289900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3307500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2676400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2708300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2748400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2773400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2832300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2867500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2902100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2934000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2394600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2460600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2521700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2552400</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>772000</v>
+      </c>
+      <c r="E62" s="3">
         <v>829600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>801100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>802000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>781500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>875700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>823100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>808700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>787700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>823100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>824900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>735000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>743900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>801600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>830900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>807600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>783900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>727500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>706600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>713600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>618700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>630800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>612200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>629200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>644200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>793000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>682600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>706800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>724600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>730200</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12193900</v>
+      </c>
+      <c r="E66" s="3">
         <v>12205000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11915200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11706100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11547800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12259000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12022500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11317000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10538100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10279400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9538000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8131000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7839200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8156200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7660300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8513900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8536900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8013900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8132200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7983900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7862300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7888600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8046000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7804400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7641800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7899900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6696200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6668100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6542700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6737500</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8192700</v>
+      </c>
+      <c r="E72" s="3">
         <v>7936800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7665300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7425600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7210800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6985500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6736600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6474400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6256400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6031400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5797400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5601200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5416900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5207100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5018300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4859800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4712700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4477200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4251400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3989800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3817700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3515700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3358000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3181100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2958900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2676200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2473400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2342400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2218700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2123300</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3282400</v>
+      </c>
+      <c r="E76" s="3">
         <v>3059500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3263400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2881900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2541500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2227100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2687700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2904400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2866600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3175000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3488800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3296500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3355400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2937800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2966400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2796200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3711600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3900300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3843400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3531000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3340200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3562200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3439100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3888100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3676500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3430400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3405500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3341800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3084000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3178500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>255900</v>
+      </c>
+      <c r="E81" s="3">
         <v>271500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>239700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>214800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>225300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>248900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>262200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>218000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>225000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>234000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>196200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>184200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>209900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>188800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>158500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>147100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>235500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>225800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>261700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>172100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>302000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>157700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>176900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>174900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>282700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>202800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>131000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>123700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>95400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>129600</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>83900</v>
+      </c>
+      <c r="E83" s="3">
         <v>84800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>83700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>84200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>89800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>77200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>78500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>76800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>75000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>74200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>69200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>65700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>64700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>63500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>62200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>64500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>68500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>67300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>70900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>67400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>66100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>65600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>67300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>70200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>64500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>67500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>63200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>63300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>59900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>55700</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1197300</v>
+      </c>
+      <c r="E89" s="3">
         <v>77200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>499000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>327700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>316200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>396800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>154100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-112300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>597500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>243100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>278600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>77900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>257900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>412500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>382100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>420000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>370900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>241100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>252500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>297500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>348000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>280300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>74400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>200700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>248500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>223900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>134200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>73500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>301600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>192200</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-36700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-38200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-42200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-36700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-43800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-41000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-35200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-31400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-37100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-28700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-23400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-18600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-18300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-26500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-16700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-17500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-14500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-25100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-21700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-19400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-15200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-20600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-16900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-29600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-17100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-35100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-144400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-42200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-159000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-167400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-33100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-67300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-94100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-458700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-99800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-63200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-31600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-37300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-18600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-18700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-140200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-100600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-268400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-14500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>45000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-21700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-26900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-22700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-156200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-299100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-21400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-21100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1333600</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-396800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-259600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-24100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-217700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-271100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-162500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>172200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-49800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-235300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>220600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>375300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-16600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-194900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-189500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-718000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-314500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-49700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-108900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>121400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-272900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-221500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-251600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-99000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>317900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-86900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>19100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-222400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1094700</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-68800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>29300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>43800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-122400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-26200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>68100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-26300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-55300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>73700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-43100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>74400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-6400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-209900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>28300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-54300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>10600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-78800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>12700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>18500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>10000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>19800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>8400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-44200</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>826000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-395700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>441800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-19800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-55600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>267000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-161300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>241800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-50400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>627800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-45100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>105800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>179500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-360900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-123000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>209400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-22700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>116100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>7700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>176300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-37100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>91600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>112600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>252700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>30600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>91200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>69600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-87700</v>
       </c>
     </row>
